--- a/model_info/det_gemini_pet.xlsx
+++ b/model_info/det_gemini_pet.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="5.5" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.4431216931216931</v>
+        <v>0.655771372876636</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.6929281580766228</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7981566820276498</v>
       </c>
     </row>
     <row r="3">
@@ -638,7 +638,7 @@
         <v>1.0</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>1.0</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.6904761904761904</v>
+        <v>0.8452380952380951</v>
       </c>
     </row>
     <row r="8">
@@ -834,7 +834,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.9666666666666666</v>
+        <v>0.9833333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -932,7 +932,7 @@
         <v>1.0</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="13">
@@ -1275,7 +1275,7 @@
         <v>0.7793137720451229</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.5228451736623996</v>
+        <v>0.7566148945235075</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1324,7 @@
         <v>0.3419367856585985</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.20823839484379683</v>
+        <v>0.5927555610582621</v>
       </c>
     </row>
     <row r="21">
@@ -1471,7 +1471,7 @@
         <v>1.0</v>
       </c>
       <c r="O23" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="24">
@@ -1520,7 +1520,7 @@
         <v>0.9444444444444444</v>
       </c>
       <c r="O24" s="0" t="n">
-        <v>0.9505494505494506</v>
+        <v>0.9752747252747254</v>
       </c>
     </row>
     <row r="25">
@@ -1569,7 +1569,7 @@
         <v>1.0</v>
       </c>
       <c r="O25" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9255514705882353</v>
       </c>
     </row>
     <row r="26">
@@ -1716,7 +1716,7 @@
         <v>0.8330325165938083</v>
       </c>
       <c r="O28" s="0" t="n">
-        <v>0.8045876942393906</v>
+        <v>0.9022938471196953</v>
       </c>
     </row>
     <row r="29">
@@ -1863,7 +1863,7 @@
         <v>1.0</v>
       </c>
       <c r="O31" s="0" t="n">
-        <v>0.797979797979798</v>
+        <v>0.898989898989899</v>
       </c>
     </row>
     <row r="32">
@@ -1912,7 +1912,7 @@
         <v>0.6213177031937813</v>
       </c>
       <c r="O32" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="33">
@@ -1961,7 +1961,7 @@
         <v>0.6427163205979397</v>
       </c>
       <c r="O33" s="0" t="n">
-        <v>0.45239130434782604</v>
+        <v>0.6820780051150894</v>
       </c>
     </row>
     <row r="34">
@@ -2108,7 +2108,7 @@
         <v>0.75</v>
       </c>
       <c r="O36" s="0" t="n">
-        <v>0.3481481481481482</v>
+        <v>0.6248937462052216</v>
       </c>
     </row>
     <row r="37">
@@ -2157,7 +2157,7 @@
         <v>0.45454545454545453</v>
       </c>
       <c r="O37" s="0" t="n">
-        <v>0.08166666666666667</v>
+        <v>0.38805555555555554</v>
       </c>
     </row>
     <row r="38">
@@ -2255,7 +2255,7 @@
         <v>0.3322569156218739</v>
       </c>
       <c r="O39" s="0" t="n">
-        <v>0.0944055944055944</v>
+        <v>0.4727347120964142</v>
       </c>
     </row>
     <row r="40">
@@ -2304,7 +2304,7 @@
         <v>1.0</v>
       </c>
       <c r="O40" s="0" t="n">
-        <v>0.6</v>
+        <v>0.7545454545454545</v>
       </c>
     </row>
     <row r="41">
@@ -2353,7 +2353,7 @@
         <v>0.36363636363636365</v>
       </c>
       <c r="O41" s="0" t="n">
-        <v>0.036458333333333336</v>
+        <v>0.3667140151515152</v>
       </c>
     </row>
     <row r="42">
@@ -2402,7 +2402,7 @@
         <v>0.693169895823115</v>
       </c>
       <c r="O42" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
     </row>
     <row r="43">
@@ -2549,7 +2549,7 @@
         <v>0.3425578147534098</v>
       </c>
       <c r="O45" s="0" t="n">
-        <v>0.3051378446115288</v>
+        <v>0.619235588972431</v>
       </c>
     </row>
   </sheetData>

--- a/model_info/det_gemini_pet.xlsx
+++ b/model_info/det_gemini_pet.xlsx
@@ -393,7 +393,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.655771372876636</v>
+        <v>0.3848162071846282</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.6929281580766228</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.7981566820276498</v>
+        <v>0.6082949308755761</v>
       </c>
     </row>
     <row r="3">
@@ -638,7 +638,7 @@
         <v>1.0</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>1.0</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.8452380952380951</v>
+        <v>0.6904761904761904</v>
       </c>
     </row>
     <row r="8">
@@ -834,7 +834,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.9666666666666666</v>
       </c>
     </row>
     <row r="11">
@@ -932,7 +932,7 @@
         <v>1.0</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="13">
@@ -1275,7 +1275,7 @@
         <v>0.7793137720451229</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.7566148945235075</v>
+        <v>0.5178178162233381</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1324,7 @@
         <v>0.3419367856585985</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.5927555610582621</v>
+        <v>0.20350570405189236</v>
       </c>
     </row>
     <row r="21">
@@ -1471,7 +1471,7 @@
         <v>1.0</v>
       </c>
       <c r="O23" s="0" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.611111111111111</v>
       </c>
     </row>
     <row r="24">
@@ -1520,7 +1520,7 @@
         <v>0.9444444444444444</v>
       </c>
       <c r="O24" s="0" t="n">
-        <v>0.9752747252747254</v>
+        <v>0.9505494505494506</v>
       </c>
     </row>
     <row r="25">
@@ -1569,7 +1569,7 @@
         <v>1.0</v>
       </c>
       <c r="O25" s="0" t="n">
-        <v>0.9255514705882353</v>
+        <v>0.8547794117647058</v>
       </c>
     </row>
     <row r="26">
@@ -1716,7 +1716,7 @@
         <v>0.8330325165938083</v>
       </c>
       <c r="O28" s="0" t="n">
-        <v>0.9022938471196953</v>
+        <v>0.8045876942393906</v>
       </c>
     </row>
     <row r="29">
@@ -1863,7 +1863,7 @@
         <v>1.0</v>
       </c>
       <c r="O31" s="0" t="n">
-        <v>0.898989898989899</v>
+        <v>0.797979797979798</v>
       </c>
     </row>
     <row r="32">
@@ -1912,7 +1912,7 @@
         <v>0.6213177031937813</v>
       </c>
       <c r="O32" s="0" t="n">
-        <v>0.6875</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="33">
@@ -1961,7 +1961,7 @@
         <v>0.6427163205979397</v>
       </c>
       <c r="O33" s="0" t="n">
-        <v>0.6820780051150894</v>
+        <v>0.4124744245524296</v>
       </c>
     </row>
     <row r="34">
@@ -2108,7 +2108,7 @@
         <v>0.75</v>
       </c>
       <c r="O36" s="0" t="n">
-        <v>0.6248937462052216</v>
+        <v>0.3139040680024287</v>
       </c>
     </row>
     <row r="37">
@@ -2157,7 +2157,7 @@
         <v>0.45454545454545453</v>
       </c>
       <c r="O37" s="0" t="n">
-        <v>0.38805555555555554</v>
+        <v>0.05671296296296296</v>
       </c>
     </row>
     <row r="38">
@@ -2255,7 +2255,7 @@
         <v>0.3322569156218739</v>
       </c>
       <c r="O39" s="0" t="n">
-        <v>0.4727347120964142</v>
+        <v>0.08034518672816544</v>
       </c>
     </row>
     <row r="40">
@@ -2304,7 +2304,7 @@
         <v>1.0</v>
       </c>
       <c r="O40" s="0" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="41">
@@ -2353,7 +2353,7 @@
         <v>0.36363636363636365</v>
       </c>
       <c r="O41" s="0" t="n">
-        <v>0.3667140151515152</v>
+        <v>0.02541035353535354</v>
       </c>
     </row>
     <row r="42">
@@ -2402,7 +2402,7 @@
         <v>0.693169895823115</v>
       </c>
       <c r="O42" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
     </row>
     <row r="43">
@@ -2549,7 +2549,7 @@
         <v>0.3425578147534098</v>
       </c>
       <c r="O45" s="0" t="n">
-        <v>0.619235588972431</v>
+        <v>0.2847953216374269</v>
       </c>
     </row>
   </sheetData>
